--- a/Programa conferencia.xlsx
+++ b/Programa conferencia.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Apoio1\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Apoio1\Desktop\Sistema Conferencia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E06938F-DEBF-4772-8437-8A855631B54E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC9C157-DB87-44B5-BA71-3933781C38C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{D9876C19-AA45-4750-98F6-B6407576DC16}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>Código do Produto</t>
   </si>
@@ -56,75 +56,6 @@
     <t>7891033903108</t>
   </si>
   <si>
-    <t>7891033906130</t>
-  </si>
-  <si>
-    <t>7891033941339</t>
-  </si>
-  <si>
-    <t>7891033941346</t>
-  </si>
-  <si>
-    <t>7891033941360</t>
-  </si>
-  <si>
-    <t>7891033941384</t>
-  </si>
-  <si>
-    <t>7891033941391</t>
-  </si>
-  <si>
-    <t>7891033941407</t>
-  </si>
-  <si>
-    <t>7891033941414</t>
-  </si>
-  <si>
-    <t>7891033941452</t>
-  </si>
-  <si>
-    <t>7891033941476</t>
-  </si>
-  <si>
-    <t>7891033941483</t>
-  </si>
-  <si>
-    <t>7891033941490</t>
-  </si>
-  <si>
-    <t>7891033941544</t>
-  </si>
-  <si>
-    <t>7891033941568</t>
-  </si>
-  <si>
-    <t>7891033941575</t>
-  </si>
-  <si>
-    <t>7891033941582</t>
-  </si>
-  <si>
-    <t>7891033941599</t>
-  </si>
-  <si>
-    <t>7891033941612</t>
-  </si>
-  <si>
-    <t>7891033941629</t>
-  </si>
-  <si>
-    <t>7891033943050</t>
-  </si>
-  <si>
-    <t>7891033943494</t>
-  </si>
-  <si>
-    <t>7891033945740</t>
-  </si>
-  <si>
-    <t>7891033945764</t>
-  </si>
-  <si>
     <t>7891033948154</t>
   </si>
   <si>
@@ -137,9 +68,6 @@
     <t>7891033948215</t>
   </si>
   <si>
-    <t>7891033949779</t>
-  </si>
-  <si>
     <t>7891033950935</t>
   </si>
   <si>
@@ -147,6 +75,153 @@
   </si>
   <si>
     <t>Volumes</t>
+  </si>
+  <si>
+    <t>7891033013029</t>
+  </si>
+  <si>
+    <t>7891033013173</t>
+  </si>
+  <si>
+    <t>7891033070664</t>
+  </si>
+  <si>
+    <t>7891033481439</t>
+  </si>
+  <si>
+    <t>7891033482801</t>
+  </si>
+  <si>
+    <t>7891033492459</t>
+  </si>
+  <si>
+    <t>7891033492503</t>
+  </si>
+  <si>
+    <t>7891033492527</t>
+  </si>
+  <si>
+    <t>7891033497652</t>
+  </si>
+  <si>
+    <t>7891033498789</t>
+  </si>
+  <si>
+    <t>7891033502684</t>
+  </si>
+  <si>
+    <t>7891033508815</t>
+  </si>
+  <si>
+    <t>7891033517459</t>
+  </si>
+  <si>
+    <t>7891033517466</t>
+  </si>
+  <si>
+    <t>7891033530946</t>
+  </si>
+  <si>
+    <t>7891033534357</t>
+  </si>
+  <si>
+    <t>7891033534524</t>
+  </si>
+  <si>
+    <t>7891033556755</t>
+  </si>
+  <si>
+    <t>7891033556779</t>
+  </si>
+  <si>
+    <t>7891033558056</t>
+  </si>
+  <si>
+    <t>7891033559572</t>
+  </si>
+  <si>
+    <t>7891033583720</t>
+  </si>
+  <si>
+    <t>7891033591886</t>
+  </si>
+  <si>
+    <t>7891033594368</t>
+  </si>
+  <si>
+    <t>7891033740437</t>
+  </si>
+  <si>
+    <t>7891033820610</t>
+  </si>
+  <si>
+    <t>7891033843879</t>
+  </si>
+  <si>
+    <t>7891033849741</t>
+  </si>
+  <si>
+    <t>7891033853083</t>
+  </si>
+  <si>
+    <t>7891033853694</t>
+  </si>
+  <si>
+    <t>7891033856060</t>
+  </si>
+  <si>
+    <t>7891033859474</t>
+  </si>
+  <si>
+    <t>7891033871261</t>
+  </si>
+  <si>
+    <t>7891033872572</t>
+  </si>
+  <si>
+    <t>7891033872930</t>
+  </si>
+  <si>
+    <t>7891033873258</t>
+  </si>
+  <si>
+    <t>7891033873401</t>
+  </si>
+  <si>
+    <t>7891033878079</t>
+  </si>
+  <si>
+    <t>7891033882038</t>
+  </si>
+  <si>
+    <t>7891033883035</t>
+  </si>
+  <si>
+    <t>7891033883042</t>
+  </si>
+  <si>
+    <t>7891033893317</t>
+  </si>
+  <si>
+    <t>7891033896806</t>
+  </si>
+  <si>
+    <t>7891033896813</t>
+  </si>
+  <si>
+    <t>7891033910007</t>
+  </si>
+  <si>
+    <t>7891033930470</t>
+  </si>
+  <si>
+    <t>7891033935413</t>
+  </si>
+  <si>
+    <t>7891033935482</t>
+  </si>
+  <si>
+    <t>7891033947584</t>
   </si>
 </sst>
 </file>
@@ -518,7 +593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14B8BA79-486A-4311-9DC6-50AF49FF2C77}">
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
@@ -532,334 +607,334 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>84982</v>
+        <v>1302</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C2">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>90310</v>
+        <v>1317</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>90613</v>
+        <v>7066</v>
       </c>
       <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4">
         <v>4</v>
-      </c>
-      <c r="C4">
-        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>94133</v>
+        <v>48143</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C5">
-        <v>51</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>94134</v>
+        <v>48280</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C6">
-        <v>51</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>94136</v>
+        <v>49245</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C7">
-        <v>64</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>94138</v>
+        <v>49250</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C8">
-        <v>49</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>94139</v>
+        <v>49252</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C9">
-        <v>110</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>94140</v>
+        <v>49765</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C10">
-        <v>49</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>94141</v>
+        <v>49878</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C11">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>94145</v>
+        <v>50268</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C12">
-        <v>114</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>94147</v>
+        <v>50881</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C13">
-        <v>83</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>94148</v>
+        <v>51745</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C14">
-        <v>87</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>94149</v>
+        <v>51746</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C15">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>94154</v>
+        <v>53094</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C16">
-        <v>88</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>94156</v>
+        <v>53435</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C17">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>94157</v>
+        <v>53452</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C18">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>94158</v>
+        <v>55675</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C19">
-        <v>81</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>94159</v>
+        <v>55677</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C20">
-        <v>154</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>94161</v>
+        <v>55805</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C21">
-        <v>46</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>94162</v>
+        <v>55957</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C22">
-        <v>86</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>94305</v>
+        <v>58372</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C23">
-        <v>52</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>94349</v>
+        <v>59188</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C24">
-        <v>134</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>94574</v>
+        <v>59436</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C25">
-        <v>53</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>94576</v>
+        <v>74043</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C26">
-        <v>155</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>94815</v>
+        <v>82061</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C27">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>94816</v>
+        <v>84387</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C28">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>94820</v>
+        <v>84974</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C29">
-        <v>10</v>
+        <v>115</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>94821</v>
+        <v>84982</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="C30">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>94977</v>
+        <v>85308</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <v>3</v>
@@ -867,23 +942,298 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>95093</v>
+        <v>85369</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C32">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
+        <v>85606</v>
+      </c>
+      <c r="B33" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>85947</v>
+      </c>
+      <c r="B34" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>87126</v>
+      </c>
+      <c r="B35" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>87257</v>
+      </c>
+      <c r="B36" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>87293</v>
+      </c>
+      <c r="B37" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>87325</v>
+      </c>
+      <c r="B38" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>87340</v>
+      </c>
+      <c r="B39" t="s">
+        <v>47</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>87807</v>
+      </c>
+      <c r="B40" t="s">
+        <v>48</v>
+      </c>
+      <c r="C40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>88203</v>
+      </c>
+      <c r="B41" t="s">
+        <v>49</v>
+      </c>
+      <c r="C41">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>88303</v>
+      </c>
+      <c r="B42" t="s">
+        <v>50</v>
+      </c>
+      <c r="C42">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>88304</v>
+      </c>
+      <c r="B43" t="s">
+        <v>51</v>
+      </c>
+      <c r="C43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>89331</v>
+      </c>
+      <c r="B44" t="s">
+        <v>52</v>
+      </c>
+      <c r="C44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>89680</v>
+      </c>
+      <c r="B45" t="s">
+        <v>53</v>
+      </c>
+      <c r="C45">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>89681</v>
+      </c>
+      <c r="B46" t="s">
+        <v>54</v>
+      </c>
+      <c r="C46">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>90310</v>
+      </c>
+      <c r="B47" t="s">
+        <v>3</v>
+      </c>
+      <c r="C47">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>91000</v>
+      </c>
+      <c r="B48" t="s">
+        <v>55</v>
+      </c>
+      <c r="C48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>93047</v>
+      </c>
+      <c r="B49" t="s">
+        <v>56</v>
+      </c>
+      <c r="C49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>93541</v>
+      </c>
+      <c r="B50" t="s">
+        <v>57</v>
+      </c>
+      <c r="C50">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>93548</v>
+      </c>
+      <c r="B51" t="s">
+        <v>58</v>
+      </c>
+      <c r="C51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>94758</v>
+      </c>
+      <c r="B52" t="s">
+        <v>59</v>
+      </c>
+      <c r="C52">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>94815</v>
+      </c>
+      <c r="B53" t="s">
+        <v>4</v>
+      </c>
+      <c r="C53">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>94816</v>
+      </c>
+      <c r="B54" t="s">
+        <v>5</v>
+      </c>
+      <c r="C54">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>94820</v>
+      </c>
+      <c r="B55" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>94821</v>
+      </c>
+      <c r="B56" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>95093</v>
+      </c>
+      <c r="B57" t="s">
+        <v>8</v>
+      </c>
+      <c r="C57">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58">
         <v>95094</v>
       </c>
-      <c r="B33" t="s">
-        <v>33</v>
-      </c>
-      <c r="C33">
+      <c r="B58" t="s">
+        <v>9</v>
+      </c>
+      <c r="C58">
         <v>6</v>
       </c>
     </row>
